--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488268_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488268_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5532</v>
+        <v>1.7259</v>
       </c>
       <c r="E2" t="n">
-        <v>1.1048</v>
+        <v>0.3761</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4484</v>
+        <v>1.3499</v>
       </c>
       <c r="G2" t="n">
         <v>0.2437</v>
@@ -610,13 +610,13 @@
         <v>0.9264</v>
       </c>
       <c r="S2" t="n">
-        <v>1.3831</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9774</v>
+        <v>0.2487</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4056</v>
+        <v>0.3071</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. MAIGA</t>
+          <t>A. USAOLA REDONDO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2906</v>
+        <v>1.3781</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3817</v>
+        <v>0.2701</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.0911</v>
+        <v>1.108</v>
       </c>
       <c r="G4" t="n">
-        <v>2.7042</v>
+        <v>1.2536</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2356</v>
+        <v>-0.6726</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4686</v>
+        <v>1.9262</v>
       </c>
       <c r="J4" t="n">
-        <v>5.262</v>
+        <v>0.7078</v>
       </c>
       <c r="K4" t="n">
-        <v>2.5249</v>
+        <v>-1.2413</v>
       </c>
       <c r="L4" t="n">
-        <v>2.7371</v>
+        <v>1.9492</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.5578</v>
+        <v>0.5457</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.2892</v>
+        <v>0.5687</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2686</v>
+        <v>-0.023</v>
       </c>
       <c r="P4" t="n">
-        <v>1.4823</v>
+        <v>0.9264</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.4087</v>
+        <v>0.9264</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3771</v>
+        <v>-0.4875</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6939</v>
+        <v>-0.4377</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3168</v>
+        <v>-0.0497</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.5188</v>
+        <v>-0.3144</v>
       </c>
       <c r="W4" t="n">
-        <v>-1.26</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2589</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. USAOLA REDONDO</t>
+          <t>G. MAIGA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0963</v>
+        <v>0.9125</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1607</v>
+        <v>2.6438</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9356</v>
+        <v>-1.7313</v>
       </c>
       <c r="G5" t="n">
-        <v>1.2536</v>
+        <v>2.7042</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.6726</v>
+        <v>0.2356</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9262</v>
+        <v>2.4686</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7078</v>
+        <v>5.262</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.2413</v>
+        <v>2.5249</v>
       </c>
       <c r="L5" t="n">
-        <v>1.9492</v>
+        <v>2.7371</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5457</v>
+        <v>-2.5578</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5687</v>
+        <v>-2.2892</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.023</v>
+        <v>-0.2686</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9264</v>
+        <v>1.4823</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9264</v>
+        <v>2.4087</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7692</v>
+        <v>-0.7551</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5471</v>
+        <v>-0.4318</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2221</v>
+        <v>-0.3234</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3144</v>
+        <v>-2.5188</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-1.26</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3144</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4706</v>
+        <v>0.7567</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.3441</v>
+        <v>-0.9841</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8147</v>
+        <v>1.7408</v>
       </c>
       <c r="G6" t="n">
         <v>-0.0907</v>
@@ -922,13 +922,13 @@
         <v>1.1117</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5504</v>
+        <v>-0.2643</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1279</v>
+        <v>-0.7679</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5775</v>
+        <v>0.5036</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. LOPEZ CALZADA</t>
+          <t>R. BROCO VAZQUEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3814</v>
+        <v>0.0547</v>
       </c>
       <c r="E7" t="n">
-        <v>2.3617</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.9803</v>
+        <v>0.0547</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.317</v>
+        <v>0.1306</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7536</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.0705</v>
+        <v>0.1306</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5503</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>4.4828</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.9325</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.8672</v>
+        <v>0.1306</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.7292</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.138</v>
+        <v>0.1306</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1853</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6676</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2542</v>
+        <v>-0.0759</v>
       </c>
       <c r="T7" t="n">
-        <v>0.776</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5218</v>
+        <v>-0.0759</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6294</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.8883</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2589</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. BROCO VAZQUEZ</t>
+          <t>L. LOPEZ CALZADA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0547</v>
+        <v>-0.1088</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1.6992</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0547</v>
+        <v>-1.808</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1306</v>
+        <v>-0.317</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2.7536</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1306</v>
+        <v>-3.0705</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1.5503</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>4.4828</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-2.9325</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1306</v>
+        <v>-1.8672</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-1.7292</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1306</v>
+        <v>-0.138</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.6676</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0759</v>
+        <v>-0.236</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.1135</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0759</v>
+        <v>-0.3495</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.6294</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.8883</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="9">
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5152</v>
+        <v>-0.4058</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0118</v>
+        <v>-0.9024</v>
       </c>
       <c r="F9" t="n">
         <v>0.4966</v>
@@ -1156,10 +1156,10 @@
         <v>1.4823</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8717</v>
+        <v>-0.7623</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8207</v>
+        <v>-0.7113</v>
       </c>
       <c r="U9" t="n">
         <v>-0.051</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.076</v>
+        <v>-1.1519</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5502</v>
+        <v>1.302</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.6262</v>
+        <v>-2.4538</v>
       </c>
       <c r="G10" t="n">
         <v>-0.5578</v>
@@ -1234,13 +1234,13 @@
         <v>2.2234</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.2391</v>
+        <v>-1.315</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1826</v>
+        <v>-0.4309</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0565</v>
+        <v>-0.8842</v>
       </c>
       <c r="V10" t="n">
         <v>2.2033</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.1949</v>
+        <v>-3.4623</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.7811</v>
+        <v>-2.9747</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4138</v>
+        <v>-0.4876</v>
       </c>
       <c r="G12" t="n">
         <v>-2.4703</v>
@@ -1390,13 +1390,13 @@
         <v>2.7793</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.075</v>
+        <v>-1.3424</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.4014</v>
+        <v>-0.595</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6735</v>
+        <v>-0.7474</v>
       </c>
       <c r="V12" t="n">
         <v>2.2033</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.8978</v>
+        <v>-6.1684</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.046</v>
+        <v>-5.686</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.8518</v>
+        <v>-0.4824</v>
       </c>
       <c r="G13" t="n">
         <v>-4.9081</v>
@@ -1468,13 +1468,13 @@
         <v>0.7411</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.8044</v>
+        <v>-1.075</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9302</v>
+        <v>-0.5701000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8742</v>
+        <v>-0.5049</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-8.7265</v>
+        <v>-7.358699999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.975899999999999</v>
+        <v>-3.607999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.7506</v>
+        <v>-3.750500000000001</v>
       </c>
       <c r="G14" t="n">
         <v>-3.062</v>
@@ -1531,7 +1531,7 @@
         <v>-10.7131</v>
       </c>
       <c r="N14" t="n">
-        <v>-9.255499999999998</v>
+        <v>-9.2555</v>
       </c>
       <c r="O14" t="n">
         <v>-1.4578</v>
@@ -1546,13 +1546,13 @@
         <v>14.8228</v>
       </c>
       <c r="S14" t="n">
-        <v>-7.517200000000001</v>
+        <v>-6.1493</v>
       </c>
       <c r="T14" t="n">
-        <v>-5.005100000000001</v>
+        <v>-3.6372</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.5121</v>
+        <v>-2.5123</v>
       </c>
       <c r="V14" t="n">
         <v>4.440892098500626e-16</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.4718</v>
+        <v>5.6391</v>
       </c>
       <c r="E15" t="n">
-        <v>5.9423</v>
+        <v>5.1589</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5295</v>
+        <v>0.4802</v>
       </c>
       <c r="G15" t="n">
         <v>4.2306</v>
@@ -1624,13 +1624,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>1.6223</v>
+        <v>0.7896</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9986</v>
+        <v>0.2151</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6237</v>
+        <v>0.5745</v>
       </c>
       <c r="V15" t="n">
         <v>0.063</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.7816</v>
+        <v>4.3436</v>
       </c>
       <c r="E16" t="n">
-        <v>5.2576</v>
+        <v>3.9845</v>
       </c>
       <c r="F16" t="n">
-        <v>0.524</v>
+        <v>0.3591</v>
       </c>
       <c r="G16" t="n">
         <v>-0.7134</v>
@@ -1702,13 +1702,13 @@
         <v>1.8529</v>
       </c>
       <c r="S16" t="n">
-        <v>2.6246</v>
+        <v>1.1866</v>
       </c>
       <c r="T16" t="n">
-        <v>1.7994</v>
+        <v>0.5264</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8252</v>
+        <v>0.6603</v>
       </c>
       <c r="V16" t="n">
         <v>2.2027</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. IDRIS IGENE</t>
+          <t>P. OSÉS BERNALDÉZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.0513</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8622</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1891</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4494</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1775</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2718</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0489</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0382</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0107</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4004</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1393</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2611</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.5284</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.7397</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7886</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. OSÉS BERNALDÉZ</t>
+          <t>J. NIELSEN HIDALGO MARTIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.7966</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.2485</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>0.548</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.4495</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9661999999999999</v>
+        <v>-0.1311</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.5806</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.9075</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9661999999999999</v>
+        <v>0.1503</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.7572</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-0.458</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-0.2814</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-0.1766</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.1117</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.7411</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>0.4032</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.1384</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>0.2649</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. NIELSEN HIDALGO MARTÍN</t>
+          <t>S. IDRIS IGENE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6221</v>
+        <v>0.6294</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6221</v>
+        <v>-0.215</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.8444</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6221</v>
+        <v>0.4494</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>0.1775</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6221</v>
+        <v>0.2718</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6221</v>
+        <v>0.0489</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.0382</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6221</v>
+        <v>0.0107</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>0.4004</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>0.1393</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>0.2611</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.1064</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>0.6625</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.4439</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. NIELSEN HIDALGO MARTIN</t>
+          <t>J. NIELSEN HIDALGO MARTÍN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0859</v>
+        <v>0.6221</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.437</v>
+        <v>0.6221</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3511</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4495</v>
+        <v>0.6221</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1311</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5806</v>
+        <v>0.6221</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9075</v>
+        <v>0.6221</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1503</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7572</v>
+        <v>0.6221</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.458</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2814</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1766</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3706</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1117</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7411</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4793</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5471</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0679</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. ALOGO EVUNA</t>
+          <t>P. OSES BERNALDEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1683</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.571</v>
+        <v>-1.0797</v>
       </c>
       <c r="F21" t="n">
-        <v>2.4027</v>
+        <v>1.6378</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7862</v>
+        <v>-1.9298</v>
       </c>
       <c r="H21" t="n">
-        <v>1.7984</v>
+        <v>-2.1326</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0121</v>
+        <v>0.2028</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3472</v>
+        <v>-0.4373</v>
       </c>
       <c r="K21" t="n">
-        <v>1.5285</v>
+        <v>-1.8687</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.1813</v>
+        <v>1.4314</v>
       </c>
       <c r="M21" t="n">
-        <v>0.439</v>
+        <v>-1.4925</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2699</v>
+        <v>-0.264</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1692</v>
+        <v>-1.2285</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.2234</v>
+        <v>0.7411</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.891</v>
+        <v>-1.1117</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6676</v>
+        <v>1.8529</v>
       </c>
       <c r="S21" t="n">
-        <v>0.576</v>
+        <v>0.7393</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.286</v>
+        <v>0.1549</v>
       </c>
       <c r="U21" t="n">
-        <v>0.862</v>
+        <v>0.5844</v>
       </c>
       <c r="V21" t="n">
+        <v>1.0074</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.3144</v>
+      </c>
+      <c r="X21" t="n">
         <v>0.6929999999999999</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.2589</v>
-      </c>
-      <c r="X21" t="n">
-        <v>-0.5659</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. OSES BERNALDEZ</t>
+          <t>R. ALOGO EVUNA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6525</v>
+        <v>0.5241</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6673</v>
+        <v>-1.7876</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0148</v>
+        <v>2.3117</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.9298</v>
+        <v>0.7862</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.1326</v>
+        <v>1.7984</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2028</v>
+        <v>-1.0121</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4373</v>
+        <v>0.3472</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.8687</v>
+        <v>1.5285</v>
       </c>
       <c r="L22" t="n">
-        <v>1.4314</v>
+        <v>-1.1813</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.4925</v>
+        <v>0.439</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.264</v>
+        <v>0.2699</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.2285</v>
+        <v>0.1692</v>
       </c>
       <c r="P22" t="n">
-        <v>0.7411</v>
+        <v>-2.2234</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1117</v>
+        <v>-3.891</v>
       </c>
       <c r="R22" t="n">
-        <v>1.8529</v>
+        <v>1.6676</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4713</v>
+        <v>1.2684</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4327</v>
+        <v>0.4974</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0386</v>
+        <v>0.771</v>
       </c>
       <c r="V22" t="n">
-        <v>1.0074</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="W22" t="n">
-        <v>0.3144</v>
+        <v>1.2589</v>
       </c>
       <c r="X22" t="n">
-        <v>0.6929999999999999</v>
+        <v>-0.5659</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.6654</v>
+        <v>-0.2485</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.4234</v>
+        <v>-1.1296</v>
       </c>
       <c r="F23" t="n">
-        <v>0.758</v>
+        <v>0.8811</v>
       </c>
       <c r="G23" t="n">
         <v>1.4175</v>
@@ -2248,13 +2248,13 @@
         <v>1.4823</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3432</v>
+        <v>0.7601</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0037</v>
+        <v>0.2901</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3469</v>
+        <v>0.47</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9439</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.7998</v>
+        <v>-0.987</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3096</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1094</v>
+        <v>-0.905</v>
       </c>
       <c r="G24" t="n">
         <v>-0.2669</v>
@@ -2326,13 +2326,13 @@
         <v>2.0382</v>
       </c>
       <c r="S24" t="n">
-        <v>0.8202</v>
+        <v>0.633</v>
       </c>
       <c r="T24" t="n">
-        <v>0.4937</v>
+        <v>0.102</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3265</v>
+        <v>0.531</v>
       </c>
       <c r="V24" t="n">
         <v>0.3144</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.7754</v>
+        <v>-1.2617</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.751</v>
+        <v>-1.1634</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.0244</v>
+        <v>-0.0982</v>
       </c>
       <c r="G25" t="n">
         <v>-0.4286</v>
@@ -2404,13 +2404,13 @@
         <v>0.7411</v>
       </c>
       <c r="S25" t="n">
-        <v>0.3673</v>
+        <v>0.881</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.383</v>
+        <v>0.2046</v>
       </c>
       <c r="U25" t="n">
-        <v>0.7503</v>
+        <v>0.6765</v>
       </c>
       <c r="V25" t="n">
         <v>-2.4553</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.0192</v>
+        <v>-2.2026</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.3598</v>
+        <v>-1.7723</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.6594</v>
+        <v>-0.4304</v>
       </c>
       <c r="G26" t="n">
         <v>-2.5208</v>
@@ -2482,13 +2482,13 @@
         <v>2.0382</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.4143</v>
+        <v>0.4023</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.8667</v>
+        <v>-0.2791</v>
       </c>
       <c r="U26" t="n">
-        <v>0.4524</v>
+        <v>0.6814</v>
       </c>
       <c r="V26" t="n">
         <v>-1.1959</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>8.726500000000001</v>
+        <v>9.379300000000002</v>
       </c>
       <c r="E27" t="n">
-        <v>3.750499999999999</v>
+        <v>3.7505</v>
       </c>
       <c r="F27" t="n">
-        <v>4.976000000000001</v>
+        <v>5.628699999999999</v>
       </c>
       <c r="G27" t="n">
         <v>3.062</v>
@@ -2530,7 +2530,7 @@
         <v>6.4414</v>
       </c>
       <c r="I27" t="n">
-        <v>-3.379199999999999</v>
+        <v>-3.3792</v>
       </c>
       <c r="J27" t="n">
         <v>10.7131</v>
@@ -2560,13 +2560,13 @@
         <v>12.9702</v>
       </c>
       <c r="S27" t="n">
-        <v>7.5171</v>
+        <v>8.169899999999998</v>
       </c>
       <c r="T27" t="n">
-        <v>2.5122</v>
+        <v>2.5123</v>
       </c>
       <c r="U27" t="n">
-        <v>5.0049</v>
+        <v>5.657899999999999</v>
       </c>
       <c r="V27" t="n">
         <v>-0.000199999999999978</v>
